--- a/measurements/35/Filled_2D_sections/sagittal/week35_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/35/Filled_2D_sections/sagittal/week35_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AF27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,97 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +591,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.128792385484831</v>
+        <v>3479.705215419501</v>
       </c>
       <c r="D2" t="n">
-        <v>17.54763119104432</v>
+        <v>342.5966089680081</v>
       </c>
       <c r="E2" t="n">
-        <v>13.56377527771927</v>
+        <v>264.8165649459476</v>
       </c>
       <c r="F2" t="n">
         <v>1.293712910436462</v>
@@ -525,24 +610,57 @@
         <v>0.3725513985941689</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I2" t="n">
-        <v>0.567454268292683</v>
+        <v>1.422991071428571</v>
       </c>
       <c r="J2" t="n">
-        <v>0.766673018292683</v>
+        <v>14.96837797619047</v>
       </c>
       <c r="K2" t="n">
-        <v>0.667063643292683</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>5.495298971861472</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>14.96837797619047</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6.543898809523809</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11.07886904761905</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7.95107886904762</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.422991071428571</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3.314732142857143</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.279265873015873</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>9.335782272456871</v>
+      <c r="AF2" s="2" t="n">
+        <v>3558.60544217687</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +671,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.226055919095776</v>
+        <v>3516.780045351474</v>
       </c>
       <c r="D3" t="n">
-        <v>17.780712857479</v>
+        <v>347.147251026971</v>
       </c>
       <c r="E3" t="n">
-        <v>13.57214470607478</v>
+        <v>264.9799680709839</v>
       </c>
       <c r="F3" t="n">
         <v>1.310088658981104</v>
@@ -572,24 +690,57 @@
         <v>0.3667141006260274</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6130907012195123</v>
+        <v>1.653645833333333</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7696265243902439</v>
+        <v>15.02604166666667</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6913586128048781</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>6.586268187830687</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>15.02604166666667</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6.607142857142857</v>
+      </c>
+      <c r="S3" t="n">
+        <v>11.96986607142857</v>
+      </c>
+      <c r="T3" t="n">
+        <v>8.307756696428571</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.653645833333333</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.904389880952381</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.75483630952381</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>17.20339438348282</v>
+      <c r="AF3" s="2" t="n">
+        <v>335.8757951060931</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +751,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.350386674598454</v>
+        <v>3564.172335600907</v>
       </c>
       <c r="D4" t="n">
-        <v>18.30055939569706</v>
+        <v>357.2966358207521</v>
       </c>
       <c r="E4" t="n">
-        <v>13.44846010498884</v>
+        <v>262.5651734783536</v>
       </c>
       <c r="F4" t="n">
         <v>1.360792183850721</v>
@@ -619,24 +770,57 @@
         <v>0.3508412945962466</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6401486280487805</v>
+        <v>1.806175595238095</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7377096036585367</v>
+        <v>14.40290178571428</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6889291158536586</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>6.083147321428571</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14.40290178571428</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6.543898809523809</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12.49813988095238</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8.351004464285714</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.806175595238095</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.431919642857143</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.604910714285714</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>13.27653605530902</v>
+      <c r="AF4" s="2" t="n">
+        <v>259.2085610798427</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +831,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.350386674598454</v>
+        <v>3564.172335600907</v>
       </c>
       <c r="D5" t="n">
-        <v>18.30055939569706</v>
+        <v>357.2966358207521</v>
       </c>
       <c r="E5" t="n">
-        <v>13.44846010498884</v>
+        <v>262.5651734783536</v>
       </c>
       <c r="F5" t="n">
         <v>1.360792183850721</v>
@@ -666,23 +850,56 @@
         <v>0.3508412945962466</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6401486280487805</v>
+        <v>1.806175595238095</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7377096036585367</v>
+        <v>14.40290178571428</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6889291158536586</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>6.083147321428571</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14.40290178571428</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6.543898809523809</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12.49813988095238</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8.351004464285714</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.806175595238095</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.431919642857143</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.604910714285714</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AF5" s="2" t="n">
         <v>1.295799108257846</v>
       </c>
     </row>
@@ -694,17 +911,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.41106484235574</v>
+        <v>3587.301587301587</v>
       </c>
       <c r="D6" t="n">
-        <v>18.41832588940132</v>
+        <v>359.595886412121</v>
       </c>
       <c r="E6" t="n">
-        <v>13.4139670686024</v>
+        <v>261.8917380060468</v>
       </c>
       <c r="F6" t="n">
         <v>1.373070754923236</v>
@@ -713,23 +930,56 @@
         <v>0.3486168093224436</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6486280487804879</v>
+        <v>2.423735119047619</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7259908536585367</v>
+        <v>14.17410714285714</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6873094512195123</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>6.263764880952381</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14.17410714285714</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6.408110119047619</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12.66369047619048</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8.401692708333332</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.423735119047619</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.828125</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.971354166666667</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AF6" s="2" t="n">
         <v>0.3984062483787392</v>
       </c>
     </row>
@@ -741,43 +991,73 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.539262343842951</v>
+        <v>3636.167800453515</v>
       </c>
       <c r="D7" t="n">
-        <v>16.54834915079722</v>
+        <v>323.0868167536599</v>
       </c>
       <c r="E7" t="n">
-        <v>13.44846009335867</v>
+        <v>262.5651732512883</v>
       </c>
       <c r="F7" t="n">
         <v>1.230501413241311</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4377390649250294</v>
+        <v>0.4377390649250297</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6683498475609756</v>
+        <v>2.492559523809524</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6683498475609756</v>
+        <v>13.04873511904762</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6683498475609756</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>5.741815476190475</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6.467633928571428</v>
+      </c>
+      <c r="S7" t="n">
+        <v>13.04873511904762</v>
+      </c>
+      <c r="T7" t="n">
+        <v>9.704706101190476</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.492559523809524</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.872767857142857</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.099888392857142</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>1.95</v>
+      <c r="AF7" s="2" t="n">
+        <v>9.75</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1068,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.539262343842951</v>
+        <v>3636.167800453515</v>
       </c>
       <c r="D8" t="n">
-        <v>16.54834915079722</v>
+        <v>323.0868167536599</v>
       </c>
       <c r="E8" t="n">
-        <v>13.44846009335867</v>
+        <v>262.5651732512883</v>
       </c>
       <c r="F8" t="n">
         <v>1.230501413241311</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4377390649250294</v>
+        <v>0.4377390649250297</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6683498475609756</v>
+        <v>2.492559523809524</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6683498475609756</v>
+        <v>13.04873511904762</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6683498475609756</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>5.741815476190475</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.467633928571428</v>
+      </c>
+      <c r="S8" t="n">
+        <v>13.04873511904762</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9.704706101190476</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.492559523809524</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.872767857142857</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.099888392857142</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.5671875</v>
+      <c r="AF8" s="2" t="n">
+        <v>1.834263392857143</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1145,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9.527364663890541</v>
+        <v>3631.632653061224</v>
       </c>
       <c r="D9" t="n">
-        <v>16.6173352032173</v>
+        <v>324.4336873009091</v>
       </c>
       <c r="E9" t="n">
-        <v>13.44846008754358</v>
+        <v>262.5651731377556</v>
       </c>
       <c r="F9" t="n">
         <v>1.235631075606109</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4335706658101479</v>
+        <v>0.433570665810148</v>
       </c>
       <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.174479166666667</v>
+      </c>
+      <c r="J9" t="n">
+        <v>13.17894345238095</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.793340773809524</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>13.17894345238095</v>
+      </c>
+      <c r="N9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.5027629573170732</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6750190548780488</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5621824186991869</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="n">
+        <v>9.933035714285714</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9.815848214285714</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6.515997023809524</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.174479166666667</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.915550595238095</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.081597222222222</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.659032012195122</v>
+      <c r="AF9" s="2" t="n">
+        <v>12.86681547619048</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1225,73 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.428911362284355</v>
+        <v>3594.104308390022</v>
       </c>
       <c r="D10" t="n">
-        <v>18.16258733156251</v>
+        <v>354.6028955209823</v>
       </c>
       <c r="E10" t="n">
-        <v>13.30456995382542</v>
+        <v>259.7558895746866</v>
       </c>
       <c r="F10" t="n">
         <v>1.365139000704061</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3591831758111739</v>
+        <v>0.359183175811174</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5027629573170732</v>
+        <v>1.716889880952381</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6555830792682927</v>
+        <v>12.79947916666667</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5631034044715447</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>6.122767857142858</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>8.658854166666666</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12.79947916666667</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10.41015625</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.716889880952381</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.094122023809524</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.264508928571428</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.6101673653455284</v>
+      <c r="AF10" s="2" t="n">
+        <v>5.956099846334221</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1302,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9.428911362284355</v>
+        <v>3594.104308390022</v>
       </c>
       <c r="D11" t="n">
-        <v>18.16258733156251</v>
+        <v>354.6028955209823</v>
       </c>
       <c r="E11" t="n">
-        <v>13.30456995382542</v>
+        <v>259.7558895746866</v>
       </c>
       <c r="F11" t="n">
         <v>1.365139000704061</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3591831758111739</v>
+        <v>0.359183175811174</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5027629573170732</v>
+        <v>1.716889880952381</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6555830792682927</v>
+        <v>12.79947916666667</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5631034044715447</v>
+        <v>6.122767857142858</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8.658854166666666</v>
+      </c>
+      <c r="S11" t="n">
+        <v>12.79947916666667</v>
+      </c>
+      <c r="T11" t="n">
+        <v>10.41015625</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.716889880952381</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.094122023809524</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.264508928571428</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1379,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.311421772754313</v>
+        <v>3549.319727891156</v>
       </c>
       <c r="D12" t="n">
-        <v>16.52467690735329</v>
+        <v>322.6246443816594</v>
       </c>
       <c r="E12" t="n">
-        <v>13.42478781793176</v>
+        <v>262.1030002548581</v>
       </c>
       <c r="F12" t="n">
         <v>1.230907864724755</v>
@@ -987,16 +1398,54 @@
         <v>0.428508961969202</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5289634146341463</v>
+        <v>2.925967261904762</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6555830792682927</v>
+        <v>12.79947916666667</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5922732469512195</v>
+        <v>6.608537946428571</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6.374627976190476</v>
+      </c>
+      <c r="S12" t="n">
+        <v>12.79947916666667</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9.705636160714286</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.925967261904762</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.226190476190476</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.511439732142858</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="n">
+        <v>14.35887896825397</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1456,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.311421772754313</v>
+        <v>3549.319727891156</v>
       </c>
       <c r="D13" t="n">
-        <v>16.52467690735329</v>
+        <v>322.6246443816594</v>
       </c>
       <c r="E13" t="n">
-        <v>13.42478781793176</v>
+        <v>262.1030002548581</v>
       </c>
       <c r="F13" t="n">
         <v>1.230907864724755</v>
@@ -1026,16 +1475,54 @@
         <v>0.428508961969202</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5289634146341463</v>
+        <v>2.925967261904762</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6555830792682927</v>
+        <v>12.79947916666667</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5922732469512195</v>
+        <v>6.608537946428571</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6.374627976190476</v>
+      </c>
+      <c r="S13" t="n">
+        <v>12.79947916666667</v>
+      </c>
+      <c r="T13" t="n">
+        <v>9.705636160714286</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.925967261904762</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.226190476190476</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.511439732142858</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>4.55</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1533,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.318262938726949</v>
+        <v>3551.927437641723</v>
       </c>
       <c r="D14" t="n">
-        <v>16.5508005211993</v>
+        <v>323.1346768424625</v>
       </c>
       <c r="E14" t="n">
-        <v>13.32130880181382</v>
+        <v>260.0826956544603</v>
       </c>
       <c r="F14" t="n">
         <v>1.242430512454283</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4274711566536319</v>
+        <v>0.4274711566536318</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5451600609756098</v>
+        <v>1.311383928571429</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6418635670731707</v>
+        <v>12.53162202380952</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5935118140243902</v>
+        <v>5.95899470899471</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6.376488095238095</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12.53162202380952</v>
+      </c>
+      <c r="T14" t="n">
+        <v>9.719122023809524</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.311383928571429</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.908110119047619</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.950892857142857</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>9.933035714285714</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1610,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9.338786436644854</v>
+        <v>3559.750566893424</v>
       </c>
       <c r="D15" t="n">
-        <v>17.26822036068614</v>
+        <v>337.1414451372056</v>
       </c>
       <c r="E15" t="n">
-        <v>13.1321048852874</v>
+        <v>256.3887144270397</v>
       </c>
       <c r="F15" t="n">
         <v>1.314962110912825</v>
@@ -1104,16 +1629,54 @@
         <v>0.3935547366658574</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5304878048780488</v>
+        <v>1.305803571428571</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6228086890243902</v>
+        <v>12.15959821428571</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5766482469512195</v>
+        <v>6.471974206349206</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5.093005952380952</v>
+      </c>
+      <c r="S15" t="n">
+        <v>12.15959821428571</v>
+      </c>
+      <c r="T15" t="n">
+        <v>8.512834821428569</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.048735119047619</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.816220238095238</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.305803571428571</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>9.815848214285714</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1687,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.338786436644854</v>
+        <v>3559.750566893424</v>
       </c>
       <c r="D16" t="n">
-        <v>17.26822036068614</v>
+        <v>337.1414451372056</v>
       </c>
       <c r="E16" t="n">
-        <v>13.1321048852874</v>
+        <v>256.3887144270397</v>
       </c>
       <c r="F16" t="n">
         <v>1.314962110912825</v>
@@ -1143,16 +1706,54 @@
         <v>0.3935547366658574</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5304878048780488</v>
+        <v>1.305803571428571</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6228086890243902</v>
+        <v>12.15959821428571</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5766482469512195</v>
+        <v>6.471974206349206</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5.093005952380952</v>
+      </c>
+      <c r="S16" t="n">
+        <v>12.15959821428571</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8.512834821428569</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3.048735119047619</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.816220238095238</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.305803571428571</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>6.515997023809524</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1764,73 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.317965496728139</v>
+        <v>3551.814058956916</v>
       </c>
       <c r="D17" t="n">
-        <v>17.10167334428648</v>
+        <v>333.8898129122597</v>
       </c>
       <c r="E17" t="n">
-        <v>13.00842029873918</v>
+        <v>253.9739201182411</v>
       </c>
       <c r="F17" t="n">
         <v>1.314661807625022</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4003628281137667</v>
+        <v>0.4003628281137668</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5162919207317074</v>
+        <v>1.372767857142857</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6040396341463414</v>
+        <v>11.79315476190476</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5601657774390244</v>
+        <v>6.245659722222221</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4.665178571428571</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11.79315476190476</v>
+      </c>
+      <c r="T17" t="n">
+        <v>8.28031994047619</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.607886904761905</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.548363095238095</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.372767857142857</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>6.030701754385965</v>
       </c>
     </row>
     <row r="18">
@@ -1202,35 +1841,73 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.279595478881619</v>
+        <v>3537.18820861678</v>
       </c>
       <c r="D18" t="n">
-        <v>16.88042777922096</v>
+        <v>329.5702566419329</v>
       </c>
       <c r="E18" t="n">
-        <v>12.97739401096251</v>
+        <v>253.3681687854585</v>
       </c>
       <c r="F18" t="n">
         <v>1.300756358708181</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4092342861146729</v>
+        <v>0.409234286114673</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5456364329268293</v>
+        <v>1.595982142857143</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5998475609756098</v>
+        <v>11.71130952380952</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5727419969512195</v>
+        <v>5.545944940476191</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.577752976190476</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11.71130952380952</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8.433035714285714</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.595982142857143</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.259672619047619</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.658854166666667</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>12.20482847744361</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +1918,73 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.279595478881619</v>
+        <v>3537.18820861678</v>
       </c>
       <c r="D19" t="n">
-        <v>16.88042777922096</v>
+        <v>329.5702566419329</v>
       </c>
       <c r="E19" t="n">
-        <v>12.97739401096251</v>
+        <v>253.3681687854585</v>
       </c>
       <c r="F19" t="n">
         <v>1.300756358708181</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4092342861146729</v>
+        <v>0.409234286114673</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5456364329268293</v>
+        <v>1.595982142857143</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5998475609756098</v>
+        <v>11.71130952380952</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5727419969512195</v>
+        <v>5.545944940476191</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4.577752976190476</v>
+      </c>
+      <c r="S19" t="n">
+        <v>11.71130952380952</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8.433035714285714</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.595982142857143</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.259672619047619</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.658854166666667</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>8.757650264052989</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +1995,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.19066032123736</v>
+        <v>3503.28798185941</v>
       </c>
       <c r="D20" t="n">
-        <v>16.33792437867421</v>
+        <v>318.9785235836392</v>
       </c>
       <c r="E20" t="n">
-        <v>12.89412052166171</v>
+        <v>251.7423530419667</v>
       </c>
       <c r="F20" t="n">
         <v>1.267083268783397</v>
@@ -1299,16 +2014,54 @@
         <v>0.4326760100228916</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5625</v>
+        <v>1.320684523809524</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5625</v>
+        <v>10.98214285714286</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5625</v>
+        <v>5.123511904761905</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.274553571428571</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10.98214285714286</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7.194568452380952</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.320684523809524</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.21688988095238</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.052455357142857</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>4.9</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2072,73 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.098750743604997</v>
+        <v>3468.253968253968</v>
       </c>
       <c r="D21" t="n">
-        <v>16.3438424337201</v>
+        <v>319.0940665631067</v>
       </c>
       <c r="E21" t="n">
-        <v>12.8369706113164</v>
+        <v>250.6265690780821</v>
       </c>
       <c r="F21" t="n">
         <v>1.273185312063597</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4280389582673407</v>
+        <v>0.4280389582673409</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5551638719512195</v>
+        <v>1.318824404761905</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5551638719512195</v>
+        <v>10.83891369047619</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5551638719512195</v>
+        <v>4.50678228021978</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4.27641369047619</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10.83891369047619</v>
+      </c>
+      <c r="T21" t="n">
+        <v>6.306069302721089</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.318824404761905</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.168526785714286</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.407614087301587</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>2.901785714285714</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2148,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>2.726934523809524</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2170,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>1.328125</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2187,70 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>1.923581932773109</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>3.942686449579832</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>2.928071749533147</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/35/Filled_2D_sections/sagittal/week35_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/35/Filled_2D_sections/sagittal/week35_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2256,4 +2462,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week35_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3558.60544217687</v>
+      </c>
+      <c r="D10" t="n">
+        <v>46.53906486022241</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3468.253968253968</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3636.167800453515</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>335.8757951060931</v>
+      </c>
+      <c r="D11" t="n">
+        <v>14.47201064095201</v>
+      </c>
+      <c r="E11" t="n">
+        <v>318.9785235836392</v>
+      </c>
+      <c r="F11" t="n">
+        <v>359.595886412121</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.295799108257846</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05136904183469602</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.230501413241311</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.373070754923236</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3984062483787392</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.03330821332034722</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3486168093224436</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4377390649250297</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0165.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0167.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0167.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0168.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0169.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0169.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>6</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0170.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0171.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0171.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0172.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0172.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0173.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0174.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0174.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>9</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0175.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0176.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0176.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0177.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0178.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>13</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>6</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>13</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.069923755276638</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4701623459816272</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.998683343734455</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.071152846727596</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>14.35887896825396</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.6703520825390465</v>
+      </c>
+      <c r="E48" t="n">
+        <v>13.17894345238095</v>
+      </c>
+      <c r="F48" t="n">
+        <v>15.02604166666667</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>91</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8.631177230507587</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.378267619348683</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.274553571428571</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13.04873511904762</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>98</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.862001943634597</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7741510145842355</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.305803571428571</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.259672619047619</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>